--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
+++ b/ci-build/StructureDefinition-senologie-geplante-systemtherapie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3170" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3340" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: GeplanteSystemtherapie</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2265,7 +2271,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO85"/>
+  <dimension ref="A1:AQ85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.53515625" customWidth="true" bestFit="true"/>
@@ -2303,11 +2309,13 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.5625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2434,6 +2442,12 @@
       <c r="AO1" t="s" s="1">
         <v>77</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2444,14 +2458,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2463,13 +2477,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2523,39 +2537,45 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AP2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2563,10 +2583,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2575,19 +2595,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2637,13 +2657,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2664,15 +2684,21 @@
         <v>20</v>
       </c>
       <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2680,10 +2706,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2692,16 +2718,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2752,19 +2778,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2779,15 +2805,21 @@
         <v>20</v>
       </c>
       <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2795,31 +2827,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2869,19 +2901,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2896,15 +2928,21 @@
         <v>20</v>
       </c>
       <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2912,10 +2950,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2927,16 +2965,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2962,13 +3000,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2986,19 +3024,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -3013,26 +3051,32 @@
         <v>20</v>
       </c>
       <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -3044,16 +3088,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3103,19 +3147,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -3124,32 +3168,38 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AP7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -3161,16 +3211,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3220,13 +3270,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3241,21 +3291,27 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3263,10 +3319,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3278,13 +3334,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3323,29 +3379,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3360,28 +3416,34 @@
         <v>20</v>
       </c>
       <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -3393,16 +3455,16 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3452,19 +3514,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3479,50 +3541,56 @@
         <v>20</v>
       </c>
       <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3571,19 +3639,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3592,21 +3660,27 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3614,10 +3688,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3629,16 +3703,16 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3688,25 +3762,25 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>162</v>
@@ -3716,14 +3790,20 @@
       </c>
       <c r="AO12" t="s" s="2">
         <v>164</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
+        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3731,31 +3811,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3781,13 +3861,13 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -3805,25 +3885,25 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>174</v>
@@ -3832,15 +3912,21 @@
         <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3848,10 +3934,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3863,16 +3949,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3898,13 +3984,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3922,42 +4008,48 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3965,31 +4057,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3997,7 +4089,7 @@
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S15" t="s" s="2">
         <v>20</v>
@@ -4015,13 +4107,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -4039,42 +4131,48 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4082,10 +4180,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -4097,16 +4195,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4132,13 +4230,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4156,42 +4254,48 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="AO16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4199,10 +4303,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -4211,16 +4315,16 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4247,13 +4351,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -4271,42 +4375,48 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4314,31 +4424,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4388,19 +4498,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4409,21 +4519,27 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4431,10 +4547,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4443,16 +4559,16 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4503,19 +4619,19 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4524,21 +4640,27 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AP19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4546,10 +4668,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4558,19 +4680,19 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4596,47 +4718,47 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>233</v>
@@ -4646,48 +4768,54 @@
       </c>
       <c r="AO20" t="s" s="2">
         <v>235</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4713,13 +4841,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4737,25 +4865,25 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>233</v>
@@ -4765,14 +4893,20 @@
       </c>
       <c r="AO21" t="s" s="2">
         <v>235</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>237</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4780,31 +4914,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4854,25 +4988,25 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>247</v>
@@ -4882,14 +5016,20 @@
       </c>
       <c r="AO22" t="s" s="2">
         <v>249</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>251</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4897,10 +5037,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4912,16 +5052,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4971,42 +5111,48 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>258</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5014,10 +5160,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -5029,13 +5175,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5086,42 +5232,48 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5129,10 +5281,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -5141,16 +5293,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5201,25 +5353,25 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>271</v>
@@ -5229,14 +5381,20 @@
       </c>
       <c r="AO25" t="s" s="2">
         <v>273</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>275</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5244,10 +5402,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5256,16 +5414,16 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5316,42 +5474,48 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5359,10 +5523,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5374,13 +5538,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5431,42 +5595,48 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5474,10 +5644,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5486,19 +5656,19 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5524,13 +5694,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5548,42 +5718,48 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5591,10 +5767,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5606,13 +5782,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5663,19 +5839,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5684,21 +5860,27 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5706,10 +5888,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5721,16 +5903,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5756,13 +5938,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5780,25 +5962,25 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>309</v>
@@ -5808,14 +5990,20 @@
       </c>
       <c r="AO30" t="s" s="2">
         <v>311</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>313</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5823,13 +6011,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5838,16 +6026,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5897,42 +6085,48 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5940,10 +6134,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5952,16 +6146,16 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6012,42 +6206,48 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6055,10 +6255,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -6067,16 +6267,16 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6127,19 +6327,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6148,21 +6348,27 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6170,10 +6376,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6182,16 +6388,16 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6242,42 +6448,48 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6285,10 +6497,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6297,20 +6509,20 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6359,42 +6571,48 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6402,13 +6620,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -6417,16 +6635,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6452,13 +6670,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6476,19 +6694,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6497,21 +6715,27 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>346</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6519,10 +6743,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6534,13 +6758,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6591,42 +6815,48 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6634,10 +6864,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6649,16 +6879,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6708,42 +6938,48 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>360</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="AO38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6751,13 +6987,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -6766,16 +7002,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6825,42 +7061,48 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6868,10 +7110,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6883,13 +7125,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6940,13 +7182,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -6961,32 +7203,38 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6998,16 +7246,16 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7045,31 +7293,31 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7078,56 +7326,62 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7176,19 +7430,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -7197,21 +7451,27 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7219,10 +7479,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7231,20 +7491,20 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7293,19 +7553,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7314,21 +7574,27 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>393</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7336,10 +7602,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7348,20 +7614,20 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7410,19 +7676,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7431,21 +7697,27 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>399</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7453,10 +7725,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7465,22 +7737,22 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7505,13 +7777,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7529,19 +7801,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7550,21 +7822,27 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>406</v>
+        <v>392</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>408</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7572,10 +7850,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7584,16 +7862,16 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7644,19 +7922,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7665,21 +7943,27 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>406</v>
+        <v>392</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7687,10 +7971,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7699,22 +7983,22 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7763,19 +8047,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7784,21 +8068,27 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7806,10 +8096,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7818,19 +8108,19 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7856,13 +8146,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7880,19 +8170,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7901,21 +8191,27 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>430</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7923,10 +8219,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7935,22 +8231,22 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7975,13 +8271,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7999,19 +8295,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -8020,21 +8316,27 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>437</v>
+        <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>440</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8042,10 +8344,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8054,20 +8356,20 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8092,13 +8394,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -8116,19 +8418,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8137,21 +8439,27 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>446</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>449</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8159,10 +8467,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8171,22 +8479,22 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8211,13 +8519,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8235,19 +8543,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8256,21 +8564,27 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>459</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8278,10 +8592,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8290,16 +8604,16 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8350,19 +8664,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8377,15 +8691,21 @@
         <v>20</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>463</v>
+        <v>20</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>465</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8393,10 +8713,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8408,13 +8728,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8465,13 +8785,13 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
@@ -8486,32 +8806,38 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO53" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8523,16 +8849,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8570,31 +8896,31 @@
         <v>20</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8603,21 +8929,27 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8625,10 +8957,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8637,20 +8969,20 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8675,13 +9007,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8699,19 +9031,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8726,15 +9058,21 @@
         <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>473</v>
+        <v>20</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>475</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8742,10 +9080,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8754,22 +9092,22 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8818,19 +9156,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8839,21 +9177,27 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>481</v>
+        <v>458</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>483</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8861,10 +9205,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8873,22 +9217,22 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8937,19 +9281,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8958,21 +9302,27 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>489</v>
+        <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>492</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8980,10 +9330,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8992,22 +9342,22 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9056,19 +9406,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -9077,21 +9427,27 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>498</v>
+        <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>501</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9099,10 +9455,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9111,22 +9467,22 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9175,19 +9531,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9196,21 +9552,27 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>507</v>
+        <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9218,10 +9580,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9230,20 +9592,20 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9292,19 +9654,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9313,21 +9675,27 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>507</v>
+        <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9335,10 +9703,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9350,13 +9718,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9407,42 +9775,48 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>517</v>
+        <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>518</v>
+        <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>519</v>
       </c>
       <c r="AO61" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9450,10 +9824,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9465,13 +9839,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9522,13 +9896,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9543,32 +9917,38 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9580,16 +9960,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9639,19 +10019,19 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9660,56 +10040,62 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9758,19 +10144,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9779,21 +10165,27 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9801,10 +10193,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9816,16 +10208,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9875,19 +10267,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9896,21 +10288,27 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO65" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9918,10 +10316,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9933,13 +10331,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9990,13 +10388,13 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
@@ -10011,32 +10409,38 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO66" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10048,16 +10452,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10107,19 +10511,19 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -10128,56 +10532,62 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10226,19 +10636,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10247,21 +10657,27 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10269,10 +10685,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10284,13 +10700,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10341,19 +10757,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -10362,21 +10778,27 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>533</v>
+        <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10384,10 +10806,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10399,13 +10821,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10456,19 +10878,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10477,21 +10899,27 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>538</v>
+        <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10499,10 +10927,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10514,13 +10942,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10571,19 +10999,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10592,21 +11020,27 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>538</v>
+        <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO71" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10614,10 +11048,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10629,19 +11063,19 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10690,42 +11124,48 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>548</v>
+        <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>549</v>
+        <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10733,10 +11173,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10748,16 +11188,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10807,42 +11247,48 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>555</v>
+        <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>556</v>
+        <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>20</v>
+        <v>557</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>559</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10850,10 +11296,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10865,13 +11311,13 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10922,42 +11368,48 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>561</v>
+        <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>562</v>
+        <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>20</v>
+        <v>563</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>565</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10965,10 +11417,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -10980,16 +11432,16 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11039,42 +11491,48 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>568</v>
+        <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>569</v>
+        <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>20</v>
+        <v>570</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11082,10 +11540,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -11097,13 +11555,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11154,19 +11612,19 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
@@ -11175,21 +11633,27 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>574</v>
+        <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AO76" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11197,10 +11661,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -11212,13 +11676,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11269,42 +11733,48 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>578</v>
+        <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>579</v>
+        <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="AO77" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11312,10 +11782,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -11327,13 +11797,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11384,13 +11854,13 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
@@ -11405,32 +11875,38 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO78" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11442,16 +11918,16 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11501,19 +11977,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11522,56 +11998,62 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO79" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11620,19 +12102,19 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
@@ -11641,21 +12123,27 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO80" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11663,10 +12151,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11678,16 +12166,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11713,13 +12201,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11737,42 +12225,48 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>578</v>
+        <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>589</v>
+        <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>592</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11780,10 +12274,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -11795,13 +12289,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11828,13 +12322,13 @@
         <v>20</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11852,42 +12346,48 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>596</v>
+        <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>597</v>
+        <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>20</v>
+        <v>598</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>600</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11895,10 +12395,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -11910,13 +12410,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11967,53 +12467,59 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>603</v>
+        <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>596</v>
+        <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>20</v>
+        <v>598</v>
       </c>
       <c r="AO83" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -12025,16 +12531,16 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12084,19 +12590,19 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -12105,21 +12611,27 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>611</v>
+        <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO84" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12127,10 +12639,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -12142,16 +12654,16 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12201,38 +12713,44 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>617</v>
+        <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO85" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO85">
+  <autoFilter ref="A1:AQ85">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
